--- a/data/Adventurer/adventurer.xlsx
+++ b/data/Adventurer/adventurer.xlsx
@@ -2,39 +2,387 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="30720" windowHeight="13380" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="21">
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="35">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -42,15 +390,322 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -403,7 +1058,6 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -414,237 +1068,224 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="1" max="14"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" customFormat="1" s="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>##字段名称</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>adventurer_name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>role</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>level</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>hp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>base_attack</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>base_armor</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>attack_speed</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>move_speed</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>crit_rate</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>crit_dmg_multiplier</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>cdr</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>passive_trait</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" customFormat="1" s="1">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>##字段类型</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>AdventurerRole</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>string</t>
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t>(list#sep=|),int</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" customFormat="1" s="2">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>##字段备注</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>冒险者ID</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>冒险者名称</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>职业</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>等级</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>血量</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>基础攻击</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>基础护甲</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>攻击速度</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>移动速度</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>暴击率</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>暴击伤害倍率</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>冷却缩减</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>独特被动特质</t>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>被动特质ID列表(|分隔)</t>
         </is>
       </c>
     </row>
@@ -689,10 +1330,8 @@
       <c r="M4" t="n">
         <v>0</v>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>坚韧意志</t>
-        </is>
+      <c r="N4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -736,10 +1375,8 @@
       <c r="M5" t="n">
         <v>0</v>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>先手优势</t>
-        </is>
+      <c r="N5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -783,10 +1420,8 @@
       <c r="M6" t="n">
         <v>0.1</v>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>奥术亲和</t>
-        </is>
+      <c r="N6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -830,10 +1465,8 @@
       <c r="M7" t="n">
         <v>0</v>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>致命一击</t>
-        </is>
+      <c r="N7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -879,7 +1512,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>坚韧意志|破甲反击</t>
+          <t>1|6</t>
         </is>
       </c>
     </row>
@@ -926,7 +1559,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>致命一击|暴伤翻倍</t>
+          <t>4|5</t>
         </is>
       </c>
     </row>
